--- a/北総FAS状況/プランナー一覧.xlsx
+++ b/北総FAS状況/プランナー一覧.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="3em2sJfhc/J0z7iC6j/f4JYCXiDQVSEzkJznPOq0NDE="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="GAJcGQde7ehMERpicrERc9Y6KkQaC8n98DoPmFGe1dw="/>
     </ext>
   </extLst>
 </workbook>
@@ -96,73 +96,73 @@
     <t>福田　花梨</t>
   </si>
   <si>
+    <t>DX/VC</t>
+  </si>
+  <si>
+    <t>渡会　佳祐</t>
+  </si>
+  <si>
+    <t>田中　乃凪</t>
+  </si>
+  <si>
+    <t>VC/AO</t>
+  </si>
+  <si>
+    <t>田中　大也</t>
+  </si>
+  <si>
+    <t>飯田　未来</t>
+  </si>
+  <si>
+    <t>中渡瀬　理恵</t>
+  </si>
+  <si>
+    <t>石井　俊輔</t>
+  </si>
+  <si>
+    <t>須田　歩</t>
+  </si>
+  <si>
+    <t>植野　友介</t>
+  </si>
+  <si>
+    <t>初見　健太朗</t>
+  </si>
+  <si>
+    <t>渋谷　航大</t>
+  </si>
+  <si>
+    <t>FX/NX/VC</t>
+  </si>
+  <si>
+    <t>守田　ゆき</t>
+  </si>
+  <si>
+    <t>後藤　航太</t>
+  </si>
+  <si>
+    <t>NX/FX/YX/VC</t>
+  </si>
+  <si>
+    <t>外山　由佳</t>
+  </si>
+  <si>
+    <t>佐藤　凌太</t>
+  </si>
+  <si>
+    <t>岡山　純一</t>
+  </si>
+  <si>
+    <t>奥　崇晃</t>
+  </si>
+  <si>
+    <t>石井　真弓</t>
+  </si>
+  <si>
+    <t>成田くらしのデジタル館</t>
+  </si>
+  <si>
     <t>飯田　敬介</t>
-  </si>
-  <si>
-    <t>DX/VC</t>
-  </si>
-  <si>
-    <t>渡会　佳祐</t>
-  </si>
-  <si>
-    <t>田中　乃凪</t>
-  </si>
-  <si>
-    <t>VC/AO</t>
-  </si>
-  <si>
-    <t>田中　大也</t>
-  </si>
-  <si>
-    <t>飯田　未来</t>
-  </si>
-  <si>
-    <t>中渡瀬　理恵</t>
-  </si>
-  <si>
-    <t>石井　俊輔</t>
-  </si>
-  <si>
-    <t>須田　歩</t>
-  </si>
-  <si>
-    <t>植野　友介</t>
-  </si>
-  <si>
-    <t>初見　健太朗</t>
-  </si>
-  <si>
-    <t>渋谷　航大</t>
-  </si>
-  <si>
-    <t>FX/NX/VC</t>
-  </si>
-  <si>
-    <t>守田　ゆき</t>
-  </si>
-  <si>
-    <t>後藤　航太</t>
-  </si>
-  <si>
-    <t>NX/FX/YX/VC</t>
-  </si>
-  <si>
-    <t>外山　由佳</t>
-  </si>
-  <si>
-    <t>佐藤　凌太</t>
-  </si>
-  <si>
-    <t>岡山　純一</t>
-  </si>
-  <si>
-    <t>奥　崇晃</t>
-  </si>
-  <si>
-    <t>石井　真弓</t>
-  </si>
-  <si>
-    <t>成田くらしのデジタル館</t>
   </si>
   <si>
     <t>武田　翔人</t>
@@ -867,14 +867,16 @@
       <c r="B18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="4"/>
+      <c r="C18" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2">
-        <v>131864.0</v>
+        <v>132807.0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" ht="18.75" customHeight="1">
@@ -884,13 +886,11 @@
       <c r="B19" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="C19" s="4"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2">
-        <v>132807.0</v>
+        <v>132853.0</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>28</v>
@@ -903,14 +903,16 @@
       <c r="B20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="4"/>
+      <c r="C20" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2">
-        <v>132853.0</v>
+        <v>132025.0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" ht="18.75" customHeight="1">
@@ -921,12 +923,12 @@
         <v>18</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2">
-        <v>132025.0</v>
+        <v>130206.0</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>31</v>
@@ -939,13 +941,11 @@
       <c r="B22" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="C22" s="4"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2">
-        <v>130206.0</v>
+        <v>116563.0</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>32</v>
@@ -962,7 +962,7 @@
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2">
-        <v>116563.0</v>
+        <v>116735.0</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>33</v>
@@ -979,7 +979,7 @@
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2">
-        <v>116735.0</v>
+        <v>116586.0</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>34</v>
@@ -996,7 +996,7 @@
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2">
-        <v>116586.0</v>
+        <v>132817.0</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>35</v>
@@ -1013,7 +1013,7 @@
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2">
-        <v>132817.0</v>
+        <v>100538.0</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>36</v>
@@ -1030,7 +1030,7 @@
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2">
-        <v>100538.0</v>
+        <v>132870.0</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>37</v>
@@ -1043,14 +1043,16 @@
       <c r="B28" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="4"/>
+      <c r="C28" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2">
-        <v>132870.0</v>
+        <v>100882.0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" ht="18.75" customHeight="1">
@@ -1061,12 +1063,12 @@
         <v>18</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2">
-        <v>100882.0</v>
+        <v>129064.0</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>40</v>
@@ -1080,15 +1082,15 @@
         <v>18</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2">
-        <v>129064.0</v>
+        <v>129829.0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" ht="18.75" customHeight="1">
@@ -1099,12 +1101,12 @@
         <v>18</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2">
-        <v>129829.0</v>
+        <v>101258.0</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>43</v>
@@ -1117,13 +1119,11 @@
       <c r="B32" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="C32" s="4"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2">
-        <v>101258.0</v>
+        <v>100702.0</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>44</v>
@@ -1140,7 +1140,7 @@
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2">
-        <v>100702.0</v>
+        <v>130879.0</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>45</v>
@@ -1157,7 +1157,7 @@
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2">
-        <v>130879.0</v>
+        <v>116811.0</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>46</v>
@@ -1165,47 +1165,55 @@
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="2">
-        <v>1126.0</v>
+        <v>1301.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2">
-        <v>116811.0</v>
+        <v>131864.0</v>
       </c>
       <c r="G35" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" ht="18.75" customHeight="1">
+      <c r="A36" s="2">
+        <v>1301.0</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="36" ht="18.75" customHeight="1">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="2"/>
+      <c r="D36" s="1">
+        <v>1.0</v>
+      </c>
       <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
+      <c r="F36" s="2">
+        <v>101478.0</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="2">
-        <v>1301.0</v>
+        <v>1511.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C37" s="4"/>
-      <c r="D37" s="1">
-        <v>1.0</v>
-      </c>
+      <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2">
-        <v>101478.0</v>
+        <v>116579.0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38" ht="18.75" customHeight="1">
@@ -1219,10 +1227,10 @@
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2">
-        <v>116579.0</v>
+        <v>101221.0</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" ht="18.75" customHeight="1">
@@ -1236,10 +1244,10 @@
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2">
-        <v>101221.0</v>
+        <v>101815.0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" ht="18.75" customHeight="1">
@@ -1250,13 +1258,15 @@
         <v>50</v>
       </c>
       <c r="C40" s="4"/>
-      <c r="D40" s="2"/>
+      <c r="D40" s="1">
+        <v>1.0</v>
+      </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2">
-        <v>101815.0</v>
+        <v>132011.0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" ht="18.75" customHeight="1">
@@ -1266,16 +1276,18 @@
       <c r="B41" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C41" s="4"/>
+      <c r="C41" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="D41" s="1">
         <v>1.0</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2">
-        <v>132011.0</v>
+        <v>130877.0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="42" ht="18.75" customHeight="1">
@@ -1285,18 +1297,16 @@
       <c r="B42" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>55</v>
-      </c>
+      <c r="C42" s="4"/>
       <c r="D42" s="1">
         <v>1.0</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2">
-        <v>130877.0</v>
+        <v>131810.0</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43" ht="18.75" customHeight="1">
@@ -1307,15 +1317,13 @@
         <v>50</v>
       </c>
       <c r="C43" s="4"/>
-      <c r="D43" s="1">
-        <v>1.0</v>
-      </c>
+      <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2">
-        <v>131810.0</v>
+        <v>115159.0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" ht="18.75" customHeight="1">
@@ -1329,27 +1337,27 @@
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2">
-        <v>115159.0</v>
+        <v>116561.0</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="2">
-        <v>1511.0</v>
+        <v>1554.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2">
-        <v>116561.0</v>
+        <v>116413.0</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" ht="18.75" customHeight="1">
@@ -1363,10 +1371,10 @@
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2">
-        <v>116413.0</v>
+        <v>131831.0</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47" ht="18.75" customHeight="1">
@@ -1380,10 +1388,10 @@
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2">
-        <v>131831.0</v>
+        <v>101252.0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48" ht="18.75" customHeight="1">
@@ -1397,10 +1405,10 @@
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2">
-        <v>101252.0</v>
+        <v>133403.0</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" ht="18.75" customHeight="1">
@@ -1414,27 +1422,31 @@
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2">
-        <v>133403.0</v>
+        <v>116661.0</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="50" ht="18.75" customHeight="1">
       <c r="A50" s="2">
-        <v>1554.0</v>
+        <v>1556.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="2"/>
+        <v>66</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" s="1">
+        <v>1.0</v>
+      </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2">
-        <v>116661.0</v>
+        <v>116685.0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" ht="18.75" customHeight="1">
@@ -1445,17 +1457,17 @@
         <v>66</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="D51" s="1">
         <v>1.0</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2">
-        <v>116685.0</v>
+        <v>101328.0</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="52" ht="18.75" customHeight="1">
@@ -1473,10 +1485,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2">
-        <v>101328.0</v>
+        <v>130581.0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" ht="18.75" customHeight="1">
@@ -1487,38 +1499,34 @@
         <v>66</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>6</v>
+        <v>71</v>
       </c>
       <c r="D53" s="1">
         <v>1.0</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2">
-        <v>130581.0</v>
+        <v>131008.0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54" ht="18.75" customHeight="1">
       <c r="A54" s="2">
-        <v>1556.0</v>
+        <v>1568.0</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D54" s="1">
-        <v>1.0</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="C54" s="4"/>
+      <c r="D54" s="2"/>
       <c r="E54" s="2"/>
       <c r="F54" s="2">
-        <v>131008.0</v>
+        <v>100231.0</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="55" ht="18.75" customHeight="1">
@@ -1532,10 +1540,10 @@
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2">
-        <v>100231.0</v>
+        <v>101303.0</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56" ht="18.75" customHeight="1">
@@ -1549,27 +1557,27 @@
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
       <c r="F56" s="2">
-        <v>101303.0</v>
+        <v>116803.0</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="57" ht="18.75" customHeight="1">
       <c r="A57" s="2">
-        <v>1568.0</v>
+        <v>1803.0</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C57" s="4"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
       <c r="F57" s="2">
-        <v>116803.0</v>
+        <v>129024.0</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" ht="18.75" customHeight="1">
@@ -1579,14 +1587,18 @@
       <c r="B58" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C58" s="4"/>
-      <c r="D58" s="2"/>
+      <c r="C58" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" s="1">
+        <v>1.0</v>
+      </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2">
-        <v>129024.0</v>
+        <v>100929.0</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" ht="18.75" customHeight="1">
@@ -1596,18 +1608,14 @@
       <c r="B59" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D59" s="1">
-        <v>1.0</v>
-      </c>
+      <c r="C59" s="4"/>
+      <c r="D59" s="2"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2">
-        <v>100929.0</v>
+        <v>132876.0</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" ht="18.75" customHeight="1">
@@ -1621,26 +1629,9 @@
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
       <c r="F60" s="2">
-        <v>132876.0</v>
+        <v>116780.0</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="61" ht="18.75" customHeight="1">
-      <c r="A61" s="2">
-        <v>1803.0</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C61" s="4"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2">
-        <v>116780.0</v>
-      </c>
-      <c r="G61" s="2" t="s">
         <v>81</v>
       </c>
     </row>
